--- a/src/SpkSnbp/SpkSnbp.Web/wwwroot/file/Template_Nilai_Kriteria.xlsx
+++ b/src/SpkSnbp/SpkSnbp.Web/wwwroot/file/Template_Nilai_Kriteria.xlsx
@@ -1407,7 +1407,7 @@
       <c r="E41" s="5"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1" insertRows="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="fnRfHHR16cL3jMv6Nsi7omqTU56ILYaw2MxN5cVedVSBPImZfH/tHer9yNShicszYIRmW75diSnCWzdif3imHQ==" saltValue="+CbjiJECMKyPk1gKYt8gaA==" spinCount="100000" sheet="1" selectLockedCells="1" insertRows="0" objects="1"/>
   <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A2:B2"/>
@@ -1416,4 +1416,19 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<allowEditUser xmlns="https://web.wps.cn/et/2018/main" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main" hasInvisiblePropRange="0">
+  <rangeList sheetStid="1" master="" otherUserPermission="visible"/>
+</allowEditUser>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5A5607D9-04D2-4DE1-AC0E-A7772F01BC71}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="https://web.wps.cn/et/2018/main"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>